--- a/data/trans_orig/P3A_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34069</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26426</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49704</t>
+          <t>50515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44496</t>
+          <t>46804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76166</t>
+          <t>76419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>997654</t>
+          <t>997519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1016456</t>
+          <t>1016257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1264394</t>
+          <t>1263583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1287672</t>
+          <t>1288171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2269655</t>
+          <t>2269402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2301325</t>
+          <t>2299017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27222</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40679</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52009</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85478</t>
+          <t>85427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1639423</t>
+          <t>1639948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1665309</t>
+          <t>1664575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1544610</t>
+          <t>1544805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1566451</t>
+          <t>1566034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3192342</t>
+          <t>3192393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3225811</t>
+          <t>3224735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55209</t>
+          <t>55544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>86309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>54739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93180</t>
+          <t>92337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134319</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462862</t>
+          <t>465099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>496199</t>
+          <t>495864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420701</t>
+          <t>420519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>445721</t>
+          <t>445583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>892347</t>
+          <t>893880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933486</t>
+          <t>934329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110225</t>
+          <t>111528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156128</t>
+          <t>161196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128710</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211408</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271328</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3119533</t>
+          <t>3114465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3165436</t>
+          <t>3164133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3245935</t>
+          <t>3248379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3287079</t>
+          <t>3288439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6378979</t>
+          <t>6380530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6438899</t>
+          <t>6440921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68267</t>
+          <t>68482</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>73247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110923</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121566</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165999</t>
+          <t>167988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905316</t>
+          <t>905101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>933517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1225874</t>
+          <t>1225006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1263822</t>
+          <t>1263550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2144382</t>
+          <t>2142393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2188815</t>
+          <t>2188427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24954</t>
+          <t>25684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>51456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>52965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>87123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1913844</t>
+          <t>1912501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1939003</t>
+          <t>1938273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1710983</t>
+          <t>1710726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1734600</t>
+          <t>1734885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3634546</t>
+          <t>3633635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3668138</t>
+          <t>3667793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>56605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51133</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97539</t>
+          <t>98701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424243</t>
+          <t>424576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451511</t>
+          <t>451229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407498</t>
+          <t>408062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>433418</t>
+          <t>433722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842274</t>
+          <t>841112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878935</t>
+          <t>879373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105524</t>
+          <t>110115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154015</t>
+          <t>157243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134918</t>
+          <t>134866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188487</t>
+          <t>187969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257061</t>
+          <t>258618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>328754</t>
+          <t>327645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3264707</t>
+          <t>3261479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3313198</t>
+          <t>3308607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3363742</t>
+          <t>3364260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3417311</t>
+          <t>3417363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6642197</t>
+          <t>6643306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6713890</t>
+          <t>6712333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47353</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>42782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74237</t>
+          <t>76326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112627</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>704304</t>
+          <t>702046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>726184</t>
+          <t>725809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>918366</t>
+          <t>916277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>951425</t>
+          <t>949821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1631633</t>
+          <t>1629858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1671399</t>
+          <t>1669962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65678</t>
+          <t>65931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2034607</t>
+          <t>2033703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054837</t>
+          <t>2054984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1948373</t>
+          <t>1949407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1971403</t>
+          <t>1971163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3991653</t>
+          <t>3991400</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4021598</t>
+          <t>4021056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64714</t>
+          <t>64937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512304</t>
+          <t>511846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533056</t>
+          <t>532600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509727</t>
+          <t>509611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531424</t>
+          <t>530630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1029411</t>
+          <t>1029188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059807</t>
+          <t>1059244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>65710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104395</t>
+          <t>101998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85865</t>
+          <t>84928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129826</t>
+          <t>129463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160958</t>
+          <t>161786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218364</t>
+          <t>219145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3264182</t>
+          <t>3266579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3302475</t>
+          <t>3302867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3397313</t>
+          <t>3397676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3441274</t>
+          <t>3442211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6677352</t>
+          <t>6676571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6734758</t>
+          <t>6733930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66873</t>
+          <t>66469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93827</t>
+          <t>91574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121149</t>
+          <t>119755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144045</t>
+          <t>142799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179666</t>
+          <t>177149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448065</t>
+          <t>448469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471935</t>
+          <t>471169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634359</t>
+          <t>635753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661681</t>
+          <t>663934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090780</t>
+          <t>1093297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1126401</t>
+          <t>1127647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67360</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>60864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76161</t>
+          <t>74588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2221868</t>
+          <t>2220446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2257215</t>
+          <t>2255287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2175067</t>
+          <t>2175700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2203351</t>
+          <t>2202152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4404599</t>
+          <t>4406290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4449631</t>
+          <t>4451204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55146</t>
+          <t>54569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75558</t>
+          <t>74655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108586</t>
+          <t>108267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>584917</t>
+          <t>585466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611748</t>
+          <t>612087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>605317</t>
+          <t>605894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625810</t>
+          <t>626592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1198500</t>
+          <t>1198819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1231528</t>
+          <t>1232431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115667</t>
+          <t>116254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178805</t>
+          <t>177026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162773</t>
+          <t>158774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225027</t>
+          <t>221497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294902</t>
+          <t>305072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383958</t>
+          <t>387686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3271985</t>
+          <t>3273764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3335123</t>
+          <t>3334536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3427508</t>
+          <t>3431038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3489762</t>
+          <t>3493761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6719366</t>
+          <t>6715638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6808422</t>
+          <t>6798252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46804</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>75500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>997519</t>
+          <t>997467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1016257</t>
+          <t>1016792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1263583</t>
+          <t>1264065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1288171</t>
+          <t>1288632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2269402</t>
+          <t>2270321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2299017</t>
+          <t>2300922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53085</t>
+          <t>52698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85427</t>
+          <t>86329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1639948</t>
+          <t>1638976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1664575</t>
+          <t>1664169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1544805</t>
+          <t>1544886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1566034</t>
+          <t>1566182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3192393</t>
+          <t>3191491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3224735</t>
+          <t>3225122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86309</t>
+          <t>90722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92337</t>
+          <t>93039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132786</t>
+          <t>132667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465099</t>
+          <t>460686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495864</t>
+          <t>495017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420519</t>
+          <t>420961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>445583</t>
+          <t>444702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>893880</t>
+          <t>893999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934329</t>
+          <t>933627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111528</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>157176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126266</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209386</t>
+          <t>211271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269777</t>
+          <t>270028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3114465</t>
+          <t>3118485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3164133</t>
+          <t>3163906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3248379</t>
+          <t>3246385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3288439</t>
+          <t>3287811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6380530</t>
+          <t>6380279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6440921</t>
+          <t>6439036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68482</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73247</t>
+          <t>72967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111791</t>
+          <t>110967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>120752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167988</t>
+          <t>169203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>905101</t>
+          <t>905511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>933517</t>
+          <t>933404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1225006</t>
+          <t>1225830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1263550</t>
+          <t>1263830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2142393</t>
+          <t>2141178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2188427</t>
+          <t>2189629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25684</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51456</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>46590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52965</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1912501</t>
+          <t>1911937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1938273</t>
+          <t>1938565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1710726</t>
+          <t>1710211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1734885</t>
+          <t>1735059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3633635</t>
+          <t>3633068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3667793</t>
+          <t>3668093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>57654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>61404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98701</t>
+          <t>99237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424576</t>
+          <t>423527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451229</t>
+          <t>451117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408062</t>
+          <t>408740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>433722</t>
+          <t>434013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841112</t>
+          <t>840576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879373</t>
+          <t>878409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110115</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157243</t>
+          <t>159074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134866</t>
+          <t>134211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187969</t>
+          <t>184175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258618</t>
+          <t>258910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>327645</t>
+          <t>327133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3261479</t>
+          <t>3259648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308607</t>
+          <t>3311327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3364260</t>
+          <t>3368054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3417363</t>
+          <t>3418018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6643306</t>
+          <t>6643818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6712333</t>
+          <t>6712041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>46779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42782</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>73688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114402</t>
+          <t>113579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>702046</t>
+          <t>704878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>725809</t>
+          <t>726458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>916277</t>
+          <t>918824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>949821</t>
+          <t>952467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1629858</t>
+          <t>1630681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1669962</t>
+          <t>1670572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36275</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65931</t>
+          <t>68042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2033703</t>
+          <t>2034637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054984</t>
+          <t>2055213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1949407</t>
+          <t>1948481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1971163</t>
+          <t>1971194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3991400</t>
+          <t>3989289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4021056</t>
+          <t>4019861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64937</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511846</t>
+          <t>511592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532600</t>
+          <t>532438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509611</t>
+          <t>508860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530630</t>
+          <t>530911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1029188</t>
+          <t>1029788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059244</t>
+          <t>1059241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65710</t>
+          <t>65498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101998</t>
+          <t>104237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,39 +4983,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>106916</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>84962</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>132256</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>106916</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>84928</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>129463</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161786</t>
+          <t>161484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219145</t>
+          <t>220522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3266579</t>
+          <t>3264340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3302867</t>
+          <t>3303079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,42 +5096,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3420223</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3394883</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3442177</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>96,97%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3420223</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3397676</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3442211</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6676571</t>
+          <t>6675194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6733930</t>
+          <t>6734232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>45880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66469</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>114178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91574</t>
+          <t>99508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119755</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>159699</t>
+          <t>170667</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142799</t>
+          <t>152011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177149</t>
+          <t>193020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>461649</t>
+          <t>522040</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448469</t>
+          <t>508795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471169</t>
+          <t>532649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>649098</t>
+          <t>707860</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635753</t>
+          <t>693117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663934</t>
+          <t>722530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1110747</t>
+          <t>1229900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1093297</t>
+          <t>1207547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1127647</t>
+          <t>1248556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>54256</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>40108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>73963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>54043</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>66886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>108299</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74588</t>
+          <t>90638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119502</t>
+          <t>130151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2239883</t>
+          <t>2175217</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2220446</t>
+          <t>2155510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2255287</t>
+          <t>2189365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2189419</t>
+          <t>2116104</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2175700</t>
+          <t>2103261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2202152</t>
+          <t>2127750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4429302</t>
+          <t>4291321</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4406290</t>
+          <t>4269469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4451204</t>
+          <t>4308982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54569</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90041</t>
+          <t>98536</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74655</t>
+          <t>81599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108267</t>
+          <t>120486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>600368</t>
+          <t>661770</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585466</t>
+          <t>644312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612087</t>
+          <t>673741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>616677</t>
+          <t>686158</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>605894</t>
+          <t>674089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626592</t>
+          <t>696469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1217045</t>
+          <t>1347928</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1198819</t>
+          <t>1325978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1232431</t>
+          <t>1364865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>148889</t>
+          <t>160562</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116254</t>
+          <t>137555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177026</t>
+          <t>188368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>197341</t>
+          <t>216940</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158774</t>
+          <t>195511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221497</t>
+          <t>241933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>346230</t>
+          <t>377502</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305072</t>
+          <t>349433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387686</t>
+          <t>415073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3301901</t>
+          <t>3359028</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3273764</t>
+          <t>3331222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3334536</t>
+          <t>3382035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3455194</t>
+          <t>3510122</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3431038</t>
+          <t>3485129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3493761</t>
+          <t>3531551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6757094</t>
+          <t>6869150</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6715638</t>
+          <t>6831579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6798252</t>
+          <t>6897219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
